--- a/doctors.xlsx
+++ b/doctors.xlsx
@@ -425,28 +425,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Doctor name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Room</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dr. Ahmed</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Programming 101</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ahmed@psau.edu.sa</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>E-101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dr. Sarah</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data Structures</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sarah@psau.edu.sa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>E-102</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dr. Khalid</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Database Systems</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>khalid@psau.edu.sa</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>E-201</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dr. Reem</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>reem@psau.edu.sa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>E-205</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dr. Fahad</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>fahad@psau.edu.sa</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>E-301</t>
         </is>
       </c>
     </row>
